--- a/out/James W Bloomer Speech Logs 2025 Aug to 2026 Feb_cleaned.xlsx
+++ b/out/James W Bloomer Speech Logs 2025 Aug to 2026 Feb_cleaned.xlsx
@@ -481,20 +481,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -515,40 +516,45 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Provider Electronic Signature</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Day of Week</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Session Type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Actual Description</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Progress Code</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Service Location</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Goal Category</t>
         </is>
@@ -572,40 +578,45 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>08/27/2025</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>back to school rapport building, producing sentences to respond to when, why questions given visual supports. used mini schedule.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Expressive</t>
         </is>
@@ -629,40 +640,45 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>09/03/2025</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Articulation: Given models and visual supports, James will produce target phonemes /l, l-blend, r, th/ in 8 out of 10 opportunities as measured by SLP data collection by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026.</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>answering when, why given a field of 4 answer choices and no sentence starters. using mini schedule and reinforcement. 15/20 when, 10/20 why. Using functional words to practice /l/ (e.g. lunch, like, look, listen, plant, laptop, umbrella). Given models.</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -686,40 +702,45 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
+          <t>09/08/2025</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>producing sentences using sentence starter + visual answer choices (field of 8) to describe 16/20 past tense forms with visual/verbal/tactile prompting + mini schedule and reinforcement system. theme: functional items</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Receptive</t>
         </is>
@@ -743,24 +764,24 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>A - Student Absent</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
@@ -777,6 +798,11 @@
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -800,40 +826,45 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
+          <t>09/15/2025</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>answering function questions 10/10. answering where/who from a field of 3, 15/20. using mini schedule and reinforcement system</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -857,40 +888,45 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
+          <t>09/17/2025</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>answering where/when given a sentence starter and a field of 4 answer choices with pronoun forms "i/you/he/she), given models as needed, using mini schedule and reinforcement 20/30</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -914,24 +950,24 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>09/24/2025</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>A - Student Absent</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
@@ -948,6 +984,11 @@
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -971,40 +1012,45 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
+          <t>09/24/2025</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Answering wh-questions (e.g. when, why) using a sentence given a field of answer choices, models as needed, mini schedule, reinforcement. 20/30</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1028,40 +1074,45 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>09/29/2025</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>answering mixed wh- questions given a field of 3 answer choices. when 20/30. why 13/15 given reinforcement system, mini schedule.</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1085,40 +1136,45 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Articulation: Given models and visual supports, James will produce target phonemes /l, l-blend, r, th/ in 8 out of 10 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Predicting/using future tense in sentences given sentence starters (he will...she will...they will) paired with a photograph. 12/20 with models as needed. Cues for /l/ words (e.g. laundry, look, like, light) needed given an initial model 7/10</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1142,40 +1198,45 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t>10/08/2025</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - pm Articulation: Given models and visual supports, James will produce target phonemes /l, l-blend, r, th/ in 8 out of 10 opportunities as measured by SLP data collection by January 2026. Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>present tense forms with sentence starters (he will...she will...they will) given photos. 10/15 with an initial model. articulation /l/ 5/10 with models, /r/ 4/10 with models</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1199,40 +1260,45 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t>10/13/2025</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>answering "when" questions given a field of 8 answer choices 8/10 using sentence starters, mini schedules, and reinforcement.</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1256,40 +1322,45 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
+          <t>10/15/2025</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>answering why given a sentence starter and a field of 3 answer choices, modeled responses. 15/20 given reinforcement</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1313,40 +1384,45 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
+          <t>10/22/2025</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Articulation: Given models and visual supports, James will produce target phonemes /l, l-blend, r, th/ in 8 out of 10 opportunities as measured by SLP data collection by January 2026. Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>describing using sentence starters and a visual word bank of 12 options. 16/20 with models as needed, mini schedule and reinforcement /r/ initial 6/10 with models in functional words</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1370,40 +1446,45 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
+          <t>10/29/2025</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>answering why using complete sentences given a visual support and sentence starters 20/30 using mini schedule and reinforcement</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1427,36 +1508,41 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>10/30/2025</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Start 10:00am - End 10:30am</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>answering why, how with a visual support and sentence starters 15/20</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Expressive</t>
         </is>
@@ -1480,40 +1566,45 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
+          <t>11/05/2025</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>What will happen next predicting using sentences in future tense (e.g. he will...she will...they will) given a visual and model if needed, 12/20</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1537,40 +1628,45 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>answering "why" in sentences given 20 answer choices. 15/20 with sentence starters and mini schedule</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1594,24 +1690,24 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>11/13/2025</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>D - Clinician/Therapist Absent</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
@@ -1628,6 +1724,11 @@
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -1651,36 +1752,41 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
+          <t>11/13/2025</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Start 11:00am - End 11:30am</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Articulation: Given models and visual supports, James will produce target phonemes /l, l-blend, r, th/ in 8 out of 10 opportunities as measured by SLP data collection by January 2026. Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>answering when (today/tomorrow/yesterday) with visuals and 1 sentence verbal prompt per picture 10/15 given models as needed. /r/ in isolated trials 1/5 with models</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1704,40 +1810,45 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Articulation: Given models and visual supports, James will produce target phonemes /l, l-blend, r, th/ in 8 out of 10 opportunities as measured by SLP data collection by January 2026. Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026.</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>when, why mixed wh- questions with a field of two answer choices 33/40 with 2 sentence prompt per item. /th/ in words given model and verbal cue 6/10</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1761,40 +1872,45 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
+          <t>11/19/2025</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Articulation: Given models and visual supports, James will produce target phonemes /l, l-blend, r, th/ in 8 out of 10 opportunities as measured by SLP data collection by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026.</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>answering why from a field of 3 visually presented answer choices with sentence starters 12/20 /l/ at the sentence level 7/10 with an initial reminder</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1818,40 +1934,45 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
+          <t>12/01/2025</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Articulation: Given models and visual supports, James will produce target phonemes /l, l-blend, r, th/ in 8 out of 10 opportunities as measured by SLP data collection by January 2026. Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026.</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>noun + verb sentence formation to match a given photograph 15/20 with picture symbols F:6, models, verbal prompting, phonemic cues</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1875,24 +1996,24 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>12/05/2025</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>D - Clinician/Therapist Absent</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
@@ -1909,6 +2030,11 @@
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -1932,36 +2058,41 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
+          <t>12/05/2025</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026. Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>inferencing "why" questions 14/20 with sentence starters and visual stimuli</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>Multiple Goals</t>
         </is>
@@ -1985,40 +2116,45 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>answering why-questions from a field of 3 given verbal prompting 40/50</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Expressive</t>
         </is>
@@ -2042,40 +2178,45 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>E - Clinician/Therapist Unavailable</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
           <t>SLP in IEP</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -2099,36 +2240,41 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>future tense forms "he will...she will...they will" given photographs and sentence starters 10/15</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Expressive</t>
         </is>
@@ -2152,40 +2298,45 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>selecting past vs future tense picture from orally presented sentences, field of 6, given photographs to match. 12/16 with models as needed</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>Receptive</t>
         </is>
@@ -2209,40 +2360,45 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
+          <t>12/17/2025</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 6 answer choices, James will select a picture that correlates/matches a 1-2 sentence verbal prompt (including past tense, present tense, and future tense verbs) as measured by SLP data collection on 4 out of 5 trials by January 2026. Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026.</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>answering when questions given pictures and models 17/25</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>Receptive</t>
         </is>
@@ -2266,40 +2422,45 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>12/22/2025</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>C - Student Unavailable</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
           <t>unavailable - grade level earned extra recess</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -2323,24 +2484,24 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>A - Student Absent</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
@@ -2357,6 +2518,11 @@
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -2380,24 +2546,24 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>A - Student Absent</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
@@ -2414,6 +2580,11 @@
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -2437,40 +2608,45 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>01/14/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>D - Clinician/Therapist Absent</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
           <t>SLP Absent - will make up Thursday 1/15</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -2494,40 +2670,45 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
+          <t>01/14/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>Speech/Language - Receptive: Given a field of 4 answer choices (picture symbol + word), James will discriminate wh-question forms by selecting a response to abstract wh- questions (e.g. when, why) on 4 out of 5 opportunities as measured by SLP data collection by January 2026.</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>answering mixed wh- questions (e.g. when (yesterday/tomorrow) given a field of choices using complete sentences with a sentence starter 25/35</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
         <is>
           <t>Receptive</t>
         </is>
@@ -2551,36 +2732,41 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
+          <t>01/15/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr"/>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>Speech/Language - Articulation: Given models and visual supports, James will produce target phonemes /l, l-blend, r, th/ in 8 out of 10 opportunities as measured by SLP data collection by January 2026.</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>/th/ in initial functional words 2/5 with models, verbal prompting, repetition</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="J37" s="6" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J37" s="6" t="inlineStr">
+      <c r="K37" s="6" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K37" s="6" t="inlineStr">
+      <c r="L37" s="6" t="inlineStr">
         <is>
           <t>Articulation</t>
         </is>
@@ -2604,40 +2790,45 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>01/21/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Start 2:00pm - End 2:30pm</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>yesterday he...yesterday she... using past tense verbs 20/30</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Expressive</t>
         </is>
@@ -2661,40 +2852,45 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>B - School Closed</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
           <t>No School - MLK Day</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -2718,40 +2914,45 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>B - School Closed</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
           <t>No School - Code Red</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -2775,40 +2976,45 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>B - School Closed</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
           <t>No School - Code Red</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>(LEFT BLANK)</t>
-        </is>
-      </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>No Goal</t>
         </is>
@@ -2832,40 +3038,45 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Start 1:30pm - End 2:00pm</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>G - Groups</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Speech/Language - Expressive: Given sentence starters and a model as needed, James will use grammatically correct sentences (e.g. including pronouns, subject + verb agreement, verb tense forms) to respond to abstract wh-questions (e.g. when, why) as measured by SLP data collection in 4 out of 5 trials by January 2026.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>producing a sentence to answer past tense "what happened" given visual support and sentence starter - verbs 18/20</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>School</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Expressive</t>
         </is>
